--- a/Hardware/BOM.xlsx
+++ b/Hardware/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff\Desktop\Bottle\PCB-Design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff\Desktop\Bottle\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABA46C4-2238-4DBE-9077-5B858F836811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A102B5E7-3FCC-4A9B-A230-D52BCB342F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{24B9BE5B-F4D6-435D-A621-076E9085BD6C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="103">
   <si>
     <t>Value</t>
   </si>
@@ -454,10 +454,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>关键词：粉刺针化妆刷子PC/PVC包装管透明圆管收纳包装钻头轴承塑料包装管</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -485,29 +481,17 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>3D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="等线"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>打印，参考</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="2"/>
-      </rPr>
-      <t>3D</t>
+      <t>锂电池</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>601245-400</t>
     </r>
     <r>
       <rPr>
@@ -517,8 +501,12 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>结构件目录</t>
-    </r>
+      <t>毫安</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要焊接，仅占位，用于手动复位</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -530,8 +518,16 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>锂电池</t>
-    </r>
+      <t>触摸感应圆片</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关键词：圆形超薄铁片厚度0.3/0.5mm 电镀锌板材引磁导电防锈粉刷挂墙面网</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5*0.3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -587,7 +583,7 @@
   </si>
   <si>
     <r>
-      <t>601245-400</t>
+      <t>3D</t>
     </r>
     <r>
       <rPr>
@@ -597,12 +593,59 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>毫安</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需要焊接，仅占位，用于手动复位</t>
+      <t>打印，参考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结构件目录</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关键词：粉刺针化妆刷子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PC/PVC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包装管透明圆管收纳包装钻头轴承塑料包装管</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +653,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,8 +713,22 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -679,6 +736,7 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -721,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -752,16 +810,19 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1099,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE3DF1D-3F73-466B-A3FF-D3AF0D4441C9}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.640625" customWidth="1"/>
@@ -1434,8 +1495,8 @@
       <c r="E19" s="6">
         <v>2</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>99</v>
+      <c r="F19" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.75" x14ac:dyDescent="0.35">
@@ -1716,47 +1777,71 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="56.6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="37.75" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>93</v>
+      <c r="C36" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>92</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="38.6" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="B37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="37.299999999999997" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="C39" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
+      <c r="D39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
